--- a/data/derived_data/3_CommunityComposition/Dataset_2/ps_rare_16S_Dataset_2_otu_table.xlsx
+++ b/data/derived_data/3_CommunityComposition/Dataset_2/ps_rare_16S_Dataset_2_otu_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -35,6 +35,9 @@
     <t xml:space="preserve">LC_131</t>
   </si>
   <si>
+    <t xml:space="preserve">LC_149</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC_151</t>
   </si>
   <si>
@@ -65,9 +68,6 @@
     <t xml:space="preserve">MS_016</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_017</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_019</t>
   </si>
   <si>
@@ -95,6 +95,12 @@
     <t xml:space="preserve">MS_060</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_064</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_065</t>
   </si>
   <si>
@@ -179,37 +185,91 @@
     <t xml:space="preserve">MS_204</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_11</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_113</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_1389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_1533</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_16</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_320</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_337</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_34</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_35</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_449</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_47</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_5</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_53</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_55</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_93</t>
   </si>
 </sst>
 </file>
@@ -704,52 +764,58 @@
       <c r="BC1" t="s">
         <v>54</v>
       </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>192</v>
+        <v>553</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -761,13 +827,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -869,45 +935,51 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>674</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2035</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>836</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -916,156 +988,162 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>192</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>242</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>71</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>79</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>41</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
         <v>44</v>
       </c>
-      <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>156</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
+      <c r="BD3" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1074,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -1083,10 +1161,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1095,13 +1173,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1110,43 +1188,43 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>742</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1167,16 +1245,16 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
@@ -1197,18 +1275,24 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>863</v>
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -1241,13 +1325,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1256,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1265,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1283,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1355,27 +1439,33 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
         <v>2</v>
       </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BE5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -1456,10 +1546,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1501,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -1537,12 +1627,18 @@
         <v>0</v>
       </c>
       <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -1587,13 +1683,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2799</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1662,10 +1758,10 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -1704,108 +1800,114 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" t="n">
-        <v>448</v>
+        <v>2173</v>
       </c>
       <c r="C8" t="n">
-        <v>1156</v>
+        <v>486</v>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>1042</v>
       </c>
       <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>79</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J8" t="n">
+        <v>877</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>423</v>
+      </c>
+      <c r="M8" t="n">
+        <v>26</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>232</v>
+      </c>
+      <c r="R8" t="n">
+        <v>239</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE8" t="n">
         <v>15</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>763</v>
-      </c>
-      <c r="I8" t="n">
-        <v>234</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1253</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -1838,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
@@ -1847,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -1871,90 +1973,96 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>142</v>
       </c>
-      <c r="C9" t="n">
-        <v>833</v>
-      </c>
-      <c r="D9" t="n">
-        <v>300</v>
-      </c>
-      <c r="E9" t="n">
-        <v>97</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>147</v>
-      </c>
-      <c r="I9" t="n">
-        <v>323</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>835</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1963,31 +2071,31 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -2008,16 +2116,16 @@
         <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -2038,12 +2146,18 @@
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>102</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>118</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>845</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -2052,174 +2166,180 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1271</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2804</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2922</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2923</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2949</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2089</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2778</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2711</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2986</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2956</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2951</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2601</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2687</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2709</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2657</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1825</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1837</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1804</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1911</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2868</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2880</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1152</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1133</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>485</v>
+        <v>373</v>
       </c>
       <c r="AI10" t="n">
-        <v>2335</v>
+        <v>381</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2179</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1072</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1097</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>2555</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2485</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1595</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>934</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1711</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1573</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1983</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>2020</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
+        <v>161</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>150</v>
+      </c>
+      <c r="BE10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2231,16 +2351,16 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>577</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2264,10 +2384,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -2276,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -2372,174 +2492,3300 @@
         <v>0</v>
       </c>
       <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>449</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>259</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>97</v>
+      </c>
+      <c r="E13" t="n">
+        <v>197</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>272</v>
+      </c>
+      <c r="H13" t="n">
+        <v>813</v>
+      </c>
+      <c r="I13" t="n">
+        <v>53</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82</v>
+      </c>
+      <c r="L13" t="n">
+        <v>145</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>89</v>
+      </c>
+      <c r="P15" t="n">
+        <v>987</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>91</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>77</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>30</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>41</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>11</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>48</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="n">
+        <v>414</v>
+      </c>
+      <c r="C18" t="n">
+        <v>910</v>
+      </c>
+      <c r="D18" t="n">
         <v>65</v>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2754</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="E18" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>684</v>
+      </c>
+      <c r="J18" t="n">
+        <v>210</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>961</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>33</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" t="n">
+        <v>126</v>
+      </c>
+      <c r="C21" t="n">
+        <v>709</v>
+      </c>
+      <c r="D21" t="n">
+        <v>246</v>
+      </c>
+      <c r="E21" t="n">
+        <v>91</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>148</v>
+      </c>
+      <c r="J21" t="n">
+        <v>347</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>638</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1192</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2899</v>
+      </c>
+      <c r="G22" t="n">
+        <v>143</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2187</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>994</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2914</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2911</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2989</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2864</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1442</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2760</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2572</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2968</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2916</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2726</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2601</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2687</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1663</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1741</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1825</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1837</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1747</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1880</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1277</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1715</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>872</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>859</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>472</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>599</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>555</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>282</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1069</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1108</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2993</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1272</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1158</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>611</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>518</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2993</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>2990</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1709</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1614</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>418</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>423</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1204</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1354</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>178</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="n">
+        <v>37</v>
+      </c>
+      <c r="C25" t="n">
+        <v>128</v>
+      </c>
+      <c r="D25" t="n">
+        <v>266</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" t="n">
+        <v>527</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>288</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2322</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>22</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>721</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
         <v>399</v>
       </c>
-      <c r="W12" t="n">
+      <c r="W26" t="n">
         <v>308</v>
       </c>
-      <c r="X12" t="n">
-        <v>66</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>125</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="X26" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1164</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA26" t="n">
         <v>1157</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1186</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1079</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1244</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1104</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1343</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2370</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>2698</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2981</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1931</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1892</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>804</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>824</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1034</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1653</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1286</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1379</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2491</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>548</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>575</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>941</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>760</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1608</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1135</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>83</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>241</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>222</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>945</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>445</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>303</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>317</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" t="n">
         <v>25</v>
       </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1733</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1723</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2430</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>79</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2705</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1928</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1903</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1060</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1079</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1584</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1974</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1289</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1426</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>2558</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>2556</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>818</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>806</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2137</v>
+      <c r="C28" t="n">
+        <v>72</v>
+      </c>
+      <c r="D28" t="n">
+        <v>36</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>15</v>
+      </c>
+      <c r="G28" t="n">
+        <v>74</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>55</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>18</v>
+      </c>
+      <c r="T28" t="n">
+        <v>29</v>
+      </c>
+      <c r="U28" t="n">
+        <v>229</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>138</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>189</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>206</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>663</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>793</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>677</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>792</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>170</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>180</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
